--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561847969</v>
+        <v>46157.93070634364</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93070634364</v>
+        <v>46157.93152843095</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93152843095</v>
+        <v>46157.93393550752</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393550752</v>
+        <v>46157.93708021018</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93708021018</v>
+        <v>46158.28210559308</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210559308</v>
+        <v>46158.29665598277</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665598277</v>
+        <v>46158.29804761017</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804761017</v>
+        <v>46158.33381276315</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381276315</v>
+        <v>46158.36847820052</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847820052</v>
+        <v>46158.37281491918</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
